--- a/Processed Datasets/Results.xlsx
+++ b/Processed Datasets/Results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andyeske/Desktop/Fall 2025/Optimization Methods/Project/Processed Datasets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F914AD09-1A64-934E-A37B-5DA38E20A40C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4A339F3-4FA4-1046-B33C-B7DB32124835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="28000" windowHeight="17420" activeTab="3" xr2:uid="{7CBF7E08-C6C4-A045-9677-85FC55C6D140}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="16920" windowHeight="17420" activeTab="2" xr2:uid="{7CBF7E08-C6C4-A045-9677-85FC55C6D140}"/>
   </bookViews>
   <sheets>
     <sheet name="Problem Statistics" sheetId="5" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="51">
   <si>
     <t>A320NEO</t>
   </si>
@@ -131,9 +131,6 @@
     <t>Time (s)</t>
   </si>
   <si>
-    <t>Load Factors Sensitivity</t>
-  </si>
-  <si>
     <t>Routes</t>
   </si>
   <si>
@@ -161,24 +158,9 @@
     <t>System-wide Fuel Consumption Reduction (%)</t>
   </si>
   <si>
-    <t>Aircraft Utilization Sensitivity</t>
-  </si>
-  <si>
     <t>Passengers (million)</t>
   </si>
   <si>
-    <t>2.03s</t>
-  </si>
-  <si>
-    <t>0.94s</t>
-  </si>
-  <si>
-    <t>1.71s</t>
-  </si>
-  <si>
-    <t>132.28s</t>
-  </si>
-  <si>
     <t>LATAM Aircraft Utilization Sensitiviity</t>
   </si>
   <si>
@@ -207,6 +189,9 @@
   </si>
   <si>
     <t>Baseline Load Factor (%)</t>
+  </si>
+  <si>
+    <t>Fuel Consumption Reduction (%)</t>
   </si>
 </sst>
 </file>
@@ -272,7 +257,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="30">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -625,12 +610,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -822,6 +818,24 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1187,7 +1201,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="27" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B2" s="2">
         <v>904</v>
@@ -1204,7 +1218,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B3" s="2">
         <v>109</v>
@@ -1221,7 +1235,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B4" s="2">
         <v>131</v>
@@ -1238,7 +1252,7 @@
     </row>
     <row r="5" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="30" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B5" s="31">
         <v>5</v>
@@ -1255,7 +1269,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="27" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B6" s="2">
         <v>29.71</v>
@@ -1272,7 +1286,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="27" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B7" s="2">
         <v>30.35</v>
@@ -1289,7 +1303,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="27" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B8" s="2">
         <v>36.93</v>
@@ -1306,7 +1320,7 @@
     </row>
     <row r="9" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="30" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B9" s="39">
         <v>0.82199999999999995</v>
@@ -1323,7 +1337,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="27" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B10" s="2">
         <v>6328</v>
@@ -1340,7 +1354,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B11" s="2">
         <v>2466</v>
@@ -1357,50 +1371,54 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C12" s="28" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" s="28" t="s">
-        <v>44</v>
-      </c>
-      <c r="E12" s="29" t="s">
-        <v>45</v>
+        <v>36</v>
+      </c>
+      <c r="B12" s="53">
+        <f>'LF Sensitivity'!B10</f>
+        <v>74.66</v>
+      </c>
+      <c r="C12" s="74">
+        <f>'LF Sensitivity'!G11</f>
+        <v>3.77</v>
+      </c>
+      <c r="D12" s="74">
+        <f>'LF Sensitivity'!E12</f>
+        <v>39.630000000000003</v>
+      </c>
+      <c r="E12" s="16">
+        <f>'LF Sensitivity'!D13</f>
+        <v>257.83999999999997</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="30" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B13" s="39">
-        <v>1E-4</v>
+        <v>0</v>
       </c>
       <c r="C13" s="40">
-        <v>2.0000000000000001E-4</v>
+        <v>0</v>
       </c>
       <c r="D13" s="41">
         <v>0</v>
       </c>
       <c r="E13" s="42">
-        <v>8.0000000000000004E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="27" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B14" s="2">
         <v>994</v>
       </c>
       <c r="C14" s="28">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="D14" s="28">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="E14" s="29">
         <v>3323</v>
@@ -1408,24 +1426,24 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="27" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B15" s="2">
-        <v>979</v>
+        <v>971</v>
       </c>
       <c r="C15" s="28">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="D15" s="28">
-        <v>1329</v>
+        <v>1340</v>
       </c>
       <c r="E15" s="29">
-        <v>3231</v>
+        <v>3227</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="27" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B16" s="2">
         <v>3.3000000000000002E-2</v>
@@ -1442,7 +1460,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="27" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B17" s="2">
         <v>3.2000000000000001E-2</v>
@@ -1459,19 +1477,23 @@
     </row>
     <row r="18" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18" s="31">
-        <v>-1.54</v>
-      </c>
-      <c r="C18" s="32">
-        <v>-1.17</v>
-      </c>
-      <c r="D18" s="32">
-        <v>-2.0699999999999998</v>
-      </c>
-      <c r="E18" s="33">
-        <v>-2.77</v>
+        <v>38</v>
+      </c>
+      <c r="B18" s="17">
+        <f>'LF Sensitivity'!B3</f>
+        <v>-2.2907500000000001</v>
+      </c>
+      <c r="C18" s="73">
+        <f>'LF Sensitivity'!G4</f>
+        <v>-1.25518</v>
+      </c>
+      <c r="D18" s="73">
+        <f>'LF Sensitivity'!E5</f>
+        <v>-1.2844100000000001</v>
+      </c>
+      <c r="E18" s="18">
+        <f>'LF Sensitivity'!D6</f>
+        <v>-2.8877600000000001</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
@@ -1668,11 +1690,11 @@
         <v>1358</v>
       </c>
       <c r="C3" s="2">
-        <v>1461</v>
+        <v>1481</v>
       </c>
       <c r="D3" s="25">
         <f>(C3-B3)/B3</f>
-        <v>7.5846833578792336E-2</v>
+        <v>9.0574374079528716E-2</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="2"/>
@@ -1681,21 +1703,21 @@
         <v>1079</v>
       </c>
       <c r="I3" s="11">
-        <v>2256</v>
+        <v>2185</v>
       </c>
       <c r="J3" s="25">
         <f>(I3-H3)/H3</f>
-        <v>1.0908248378127896</v>
+        <v>1.0250231696014829</v>
       </c>
       <c r="K3" s="24">
         <v>1293</v>
       </c>
       <c r="L3" s="11">
-        <v>1794</v>
+        <v>1821</v>
       </c>
       <c r="M3" s="25">
         <f>(L3-K3)/K3</f>
-        <v>0.38747099767981441</v>
+        <v>0.40835266821345706</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
@@ -1706,11 +1728,11 @@
         <v>2025</v>
       </c>
       <c r="C4" s="11">
-        <v>2534.44</v>
+        <v>2496</v>
       </c>
       <c r="D4" s="25">
         <f t="shared" ref="D4:D21" si="0">(C4-B4)/B4</f>
-        <v>0.25157530864197536</v>
+        <v>0.2325925925925926</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="2"/>
@@ -1719,21 +1741,21 @@
         <v>1400</v>
       </c>
       <c r="I4" s="11">
-        <v>2451</v>
+        <v>2372</v>
       </c>
       <c r="J4" s="25">
         <f>(I4-H4)/H4</f>
-        <v>0.75071428571428567</v>
+        <v>0.69428571428571428</v>
       </c>
       <c r="K4" s="24">
         <v>1604</v>
       </c>
       <c r="L4" s="11">
-        <v>2463</v>
+        <v>2392</v>
       </c>
       <c r="M4" s="25">
         <f t="shared" ref="M4:M19" si="1">(L4-K4)/K4</f>
-        <v>0.53553615960099754</v>
+        <v>0.49127182044887779</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
@@ -1781,21 +1803,21 @@
         <v>1012</v>
       </c>
       <c r="I6" s="11">
-        <v>1154</v>
+        <v>1261</v>
       </c>
       <c r="J6" s="25">
         <f>(I6-H6)/H6</f>
-        <v>0.14031620553359683</v>
+        <v>0.24604743083003952</v>
       </c>
       <c r="K6" s="24">
         <v>1012</v>
       </c>
       <c r="L6" s="11">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="M6" s="25">
         <f t="shared" si="1"/>
-        <v>-0.40612648221343872</v>
+        <v>-0.40118577075098816</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
@@ -1812,21 +1834,21 @@
         <v>1369</v>
       </c>
       <c r="I7" s="11">
-        <v>973</v>
+        <v>842</v>
       </c>
       <c r="J7" s="25">
         <f>(I7-H7)/H7</f>
-        <v>-0.28926223520818117</v>
+        <v>-0.38495252008765524</v>
       </c>
       <c r="K7" s="24">
         <v>1369</v>
       </c>
       <c r="L7" s="11">
-        <v>1130</v>
+        <v>1135</v>
       </c>
       <c r="M7" s="25">
         <f t="shared" si="1"/>
-        <v>-0.17457998539079619</v>
+        <v>-0.17092768444119796</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
@@ -1837,11 +1859,11 @@
         <v>2005</v>
       </c>
       <c r="C8" s="11">
-        <v>0</v>
+        <v>496</v>
       </c>
       <c r="D8" s="25">
         <f t="shared" si="0"/>
-        <v>-1</v>
+        <v>-0.75261845386533666</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="2"/>
@@ -1853,11 +1875,11 @@
         <v>2005</v>
       </c>
       <c r="L8" s="11">
-        <v>0</v>
+        <v>331</v>
       </c>
       <c r="M8" s="25">
         <f>(L8-K8)/K8</f>
-        <v>-1</v>
+        <v>-0.83491271820448876</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
@@ -1868,11 +1890,11 @@
         <v>1970</v>
       </c>
       <c r="C9" s="11">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D9" s="25">
         <f t="shared" si="0"/>
-        <v>-0.74822335025380715</v>
+        <v>-0.74771573604060915</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="2"/>
@@ -1884,11 +1906,11 @@
         <v>1970</v>
       </c>
       <c r="L9" s="11">
-        <v>931</v>
+        <v>858</v>
       </c>
       <c r="M9" s="25">
         <f t="shared" si="1"/>
-        <v>-0.52741116751269035</v>
+        <v>-0.56446700507614211</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
@@ -1908,11 +1930,11 @@
         <v>548</v>
       </c>
       <c r="L10" s="11">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="M10" s="25">
         <f t="shared" si="1"/>
-        <v>-0.27554744525547448</v>
+        <v>-0.29014598540145986</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
@@ -1932,11 +1954,11 @@
         <v>447</v>
       </c>
       <c r="L11" s="11">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="M11" s="25">
         <f t="shared" si="1"/>
-        <v>-7.1588366890380312E-2</v>
+        <v>-9.1722595078299773E-2</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
@@ -1947,11 +1969,11 @@
         <v>388</v>
       </c>
       <c r="C12" s="11">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="D12" s="25">
         <f t="shared" si="0"/>
-        <v>0.44329896907216493</v>
+        <v>0.42783505154639173</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="2"/>
@@ -1963,11 +1985,11 @@
         <v>391</v>
       </c>
       <c r="L12" s="11">
-        <v>554</v>
+        <v>539</v>
       </c>
       <c r="M12" s="25">
         <f t="shared" si="1"/>
-        <v>0.41687979539641945</v>
+        <v>0.37851662404092073</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
@@ -1981,11 +2003,11 @@
         <v>1199</v>
       </c>
       <c r="F13" s="11">
-        <v>1890.4</v>
+        <v>1885</v>
       </c>
       <c r="G13" s="25">
         <f>(F13-E13)/E13</f>
-        <v>0.5766472060050043</v>
+        <v>0.57214345287739787</v>
       </c>
       <c r="H13" s="11"/>
       <c r="I13" s="11"/>
@@ -1994,11 +2016,11 @@
         <v>1199</v>
       </c>
       <c r="L13" s="11">
-        <v>2187</v>
+        <v>2189</v>
       </c>
       <c r="M13" s="25">
         <f t="shared" si="1"/>
-        <v>0.82402001668056712</v>
+        <v>0.82568807339449546</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
@@ -2018,11 +2040,11 @@
         <v>1587</v>
       </c>
       <c r="L14" s="11">
-        <v>825</v>
+        <v>478</v>
       </c>
       <c r="M14" s="25">
         <f t="shared" si="1"/>
-        <v>-0.48015122873345933</v>
+        <v>-0.69880277252678014</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
@@ -2042,11 +2064,11 @@
         <v>1051</v>
       </c>
       <c r="L15" s="11">
-        <v>540</v>
+        <v>0</v>
       </c>
       <c r="M15" s="25">
         <f t="shared" si="1"/>
-        <v>-0.48620361560418651</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
@@ -2060,11 +2082,11 @@
         <v>704</v>
       </c>
       <c r="F16" s="11">
-        <v>393</v>
+        <v>518</v>
       </c>
       <c r="G16" s="25">
         <f t="shared" ref="G16" si="2">(F16-E16)/E16</f>
-        <v>-0.44176136363636365</v>
+        <v>-0.26420454545454547</v>
       </c>
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
@@ -2073,11 +2095,11 @@
         <v>704</v>
       </c>
       <c r="L16" s="11">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="M16" s="25">
         <f t="shared" si="1"/>
-        <v>-0.44602272727272729</v>
+        <v>-0.43607954545454547</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
@@ -2091,11 +2113,11 @@
         <v>1013</v>
       </c>
       <c r="F17" s="11">
-        <v>795</v>
+        <v>746</v>
       </c>
       <c r="G17" s="25">
         <f>(F17-E17)/E17</f>
-        <v>-0.21520236920039487</v>
+        <v>-0.26357354392892401</v>
       </c>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
@@ -2104,11 +2126,11 @@
         <v>1013</v>
       </c>
       <c r="L17" s="11">
-        <v>1114</v>
+        <v>1126</v>
       </c>
       <c r="M17" s="25">
         <f t="shared" si="1"/>
-        <v>9.970384995064166E-2</v>
+        <v>0.11154985192497532</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
@@ -2125,21 +2147,21 @@
         <v>2347</v>
       </c>
       <c r="I18" s="11">
-        <v>326</v>
+        <v>311</v>
       </c>
       <c r="J18" s="25">
         <f>(I18-H18)/H18</f>
-        <v>-0.86109927567106948</v>
+        <v>-0.86749041329356624</v>
       </c>
       <c r="K18" s="24">
         <v>2347</v>
       </c>
       <c r="L18" s="11">
-        <v>836</v>
+        <v>681</v>
       </c>
       <c r="M18" s="25">
         <f t="shared" si="1"/>
-        <v>-0.64380059650617805</v>
+        <v>-0.70984235193864509</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
@@ -2159,11 +2181,11 @@
         <v>328</v>
       </c>
       <c r="L19" s="11">
-        <v>431</v>
+        <v>466</v>
       </c>
       <c r="M19" s="25">
         <f t="shared" si="1"/>
-        <v>0.31402439024390244</v>
+        <v>0.42073170731707316</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
@@ -2174,11 +2196,11 @@
         <v>550</v>
       </c>
       <c r="C20" s="11">
-        <v>339.50099999999998</v>
+        <v>339</v>
       </c>
       <c r="D20" s="25">
         <f t="shared" si="0"/>
-        <v>-0.38272545454545459</v>
+        <v>-0.38363636363636361</v>
       </c>
       <c r="E20" s="24"/>
       <c r="F20" s="11"/>
@@ -2190,11 +2212,11 @@
         <v>550</v>
       </c>
       <c r="L20" s="11">
-        <v>316</v>
+        <v>292</v>
       </c>
       <c r="M20" s="25">
         <f>(L20-K20)/K20</f>
-        <v>-0.42545454545454547</v>
+        <v>-0.46909090909090911</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -2202,14 +2224,14 @@
         <v>18</v>
       </c>
       <c r="B21" s="11">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C21" s="11">
-        <v>752.84500000000003</v>
+        <v>762</v>
       </c>
       <c r="D21" s="25">
         <f t="shared" si="0"/>
-        <v>-2.7332041343669216E-2</v>
+        <v>-1.6774193548387096E-2</v>
       </c>
       <c r="E21" s="24"/>
       <c r="F21" s="11"/>
@@ -2221,11 +2243,11 @@
         <v>775</v>
       </c>
       <c r="L21" s="11">
-        <v>823</v>
+        <v>796</v>
       </c>
       <c r="M21" s="25">
         <f>(L21-K21)/K21</f>
-        <v>6.1935483870967742E-2</v>
+        <v>2.7096774193548386E-2</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -2350,7 +2372,7 @@
         <v>19</v>
       </c>
       <c r="B1" s="64" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="C1" s="61"/>
       <c r="D1" s="61"/>
@@ -2408,34 +2430,34 @@
         <v>20</v>
       </c>
       <c r="B3" s="52">
-        <v>-1.54</v>
-      </c>
-      <c r="C3" s="53">
-        <v>-2.29013</v>
-      </c>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53">
-        <v>-3.0202</v>
-      </c>
-      <c r="G3" s="53"/>
-      <c r="H3" s="53">
-        <v>-3.6493099999999998</v>
-      </c>
-      <c r="I3" s="53">
-        <v>-3.6987000000000001</v>
-      </c>
-      <c r="J3" s="53">
-        <v>-4.1265299999999998</v>
-      </c>
-      <c r="K3" s="53">
-        <v>-4.1307299999999998</v>
-      </c>
-      <c r="L3" s="53">
-        <v>-4.1400699999999997</v>
+        <v>-2.2907500000000001</v>
+      </c>
+      <c r="C3" s="75">
+        <v>-3.29636</v>
+      </c>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="75">
+        <v>-4.0483500000000001</v>
+      </c>
+      <c r="G3" s="70"/>
+      <c r="H3" s="75">
+        <v>-4.7284699999999997</v>
+      </c>
+      <c r="I3" s="75">
+        <v>-5.1611500000000001</v>
+      </c>
+      <c r="J3" s="75">
+        <v>-5.3369799999999996</v>
+      </c>
+      <c r="K3" s="75">
+        <v>-5.3394599999999999</v>
+      </c>
+      <c r="L3" s="75">
+        <v>-5.3394399999999997</v>
       </c>
       <c r="M3" s="16">
-        <v>-4.1524900000000002</v>
+        <v>-5.33589</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
@@ -2443,30 +2465,30 @@
         <v>21</v>
       </c>
       <c r="B4" s="54"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53">
-        <v>-1.17</v>
-      </c>
-      <c r="H4" s="53">
-        <v>-1.23183</v>
-      </c>
-      <c r="I4" s="53">
-        <v>-1.25851</v>
-      </c>
-      <c r="J4" s="53">
-        <v>-1.2704800000000001</v>
-      </c>
-      <c r="K4" s="53">
-        <v>-1.2875399999999999</v>
-      </c>
-      <c r="L4" s="53">
-        <v>-1.2883500000000001</v>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="75">
+        <v>-1.25518</v>
+      </c>
+      <c r="H4" s="75">
+        <v>-1.2779</v>
+      </c>
+      <c r="I4" s="75">
+        <v>-1.33135</v>
+      </c>
+      <c r="J4" s="75">
+        <v>-1.33135</v>
+      </c>
+      <c r="K4" s="75">
+        <v>-1.33135</v>
+      </c>
+      <c r="L4" s="75">
+        <v>-1.33135</v>
       </c>
       <c r="M4" s="16">
-        <v>-1.2877400000000001</v>
+        <v>-1.33135</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
@@ -2474,32 +2496,32 @@
         <v>22</v>
       </c>
       <c r="B5" s="54"/>
-      <c r="C5" s="53"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="53">
-        <v>-2.0666500000000001</v>
-      </c>
-      <c r="F5" s="53">
-        <v>-2.2239800000000001</v>
-      </c>
-      <c r="G5" s="53"/>
-      <c r="H5" s="53">
-        <v>-2.2905000000000002</v>
-      </c>
-      <c r="I5" s="53">
-        <v>-2.2911000000000001</v>
-      </c>
-      <c r="J5" s="53">
-        <v>-2.29196</v>
-      </c>
-      <c r="K5" s="53">
-        <v>-2.2890299999999999</v>
-      </c>
-      <c r="L5" s="53">
-        <v>-2.2912699999999999</v>
+      <c r="C5" s="75"/>
+      <c r="D5" s="75"/>
+      <c r="E5" s="75">
+        <v>-1.2844100000000001</v>
+      </c>
+      <c r="F5" s="75">
+        <v>-1.40526</v>
+      </c>
+      <c r="G5" s="70"/>
+      <c r="H5" s="75">
+        <v>-1.4248000000000001</v>
+      </c>
+      <c r="I5" s="75">
+        <v>-1.42489</v>
+      </c>
+      <c r="J5" s="75">
+        <v>-1.42591</v>
+      </c>
+      <c r="K5" s="75">
+        <v>-1.42465</v>
+      </c>
+      <c r="L5" s="75">
+        <v>-1.4256200000000001</v>
       </c>
       <c r="M5" s="16">
-        <v>-2.2912599999999999</v>
+        <v>-1.4180600000000001</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -2509,30 +2531,30 @@
       <c r="B6" s="55"/>
       <c r="C6" s="17"/>
       <c r="D6" s="17">
-        <v>-2.77</v>
-      </c>
-      <c r="E6" s="17"/>
+        <v>-2.8877600000000001</v>
+      </c>
+      <c r="E6" s="76"/>
       <c r="F6" s="17">
-        <v>-3.1436999999999999</v>
-      </c>
-      <c r="G6" s="17"/>
+        <v>-3.6188199999999999</v>
+      </c>
+      <c r="G6" s="76"/>
       <c r="H6" s="17">
-        <v>-4.33094</v>
+        <v>-4.7140000000000004</v>
       </c>
       <c r="I6" s="17">
-        <v>-5.1932499999999999</v>
+        <v>-5.6226500000000001</v>
       </c>
       <c r="J6" s="17">
-        <v>-5.7022199999999996</v>
+        <v>-6.2093800000000003</v>
       </c>
       <c r="K6" s="17">
-        <v>-6.0513000000000003</v>
+        <v>-6.4681600000000001</v>
       </c>
       <c r="L6" s="17">
-        <v>-6.0054800000000004</v>
+        <v>-6.55037</v>
       </c>
       <c r="M6" s="18">
-        <v>-6.1531000000000002</v>
+        <v>-6.5499400000000003</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -2612,34 +2634,34 @@
         <v>20</v>
       </c>
       <c r="B10" s="52">
-        <v>3.11124</v>
-      </c>
-      <c r="C10" s="53">
-        <v>6.5781000000000001</v>
-      </c>
-      <c r="D10" s="53"/>
-      <c r="E10" s="53"/>
-      <c r="F10" s="53">
-        <v>8.8031600000000001</v>
-      </c>
-      <c r="G10" s="53"/>
-      <c r="H10" s="53">
-        <v>9.0290099999999995</v>
-      </c>
-      <c r="I10" s="53">
-        <v>32.417099999999998</v>
-      </c>
-      <c r="J10" s="53">
-        <v>9.9746699999999997</v>
-      </c>
-      <c r="K10" s="53">
-        <v>9.7350300000000001</v>
-      </c>
-      <c r="L10" s="53">
-        <v>8.3478100000000008</v>
+        <v>74.66</v>
+      </c>
+      <c r="C10" s="75">
+        <v>79.33</v>
+      </c>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="75">
+        <v>72.77</v>
+      </c>
+      <c r="G10" s="70"/>
+      <c r="H10" s="75">
+        <v>78.84</v>
+      </c>
+      <c r="I10" s="75">
+        <v>75.739999999999995</v>
+      </c>
+      <c r="J10" s="75">
+        <v>84.76</v>
+      </c>
+      <c r="K10" s="75">
+        <v>93.12</v>
+      </c>
+      <c r="L10" s="75">
+        <v>98.43</v>
       </c>
       <c r="M10" s="16">
-        <v>7.3976899999999999</v>
+        <v>87.36</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
@@ -2647,30 +2669,30 @@
         <v>21</v>
       </c>
       <c r="B11" s="54"/>
-      <c r="C11" s="53"/>
-      <c r="D11" s="53"/>
-      <c r="E11" s="53"/>
-      <c r="F11" s="53"/>
-      <c r="G11" s="53">
-        <v>0.92848399999999998</v>
-      </c>
-      <c r="H11" s="53">
-        <v>1.07857</v>
-      </c>
-      <c r="I11" s="53">
-        <v>1.0401400000000001</v>
-      </c>
-      <c r="J11" s="53">
-        <v>1.1287799999999999</v>
-      </c>
-      <c r="K11" s="53">
-        <v>1.16109</v>
-      </c>
-      <c r="L11" s="53">
-        <v>1.1448400000000001</v>
+      <c r="C11" s="75"/>
+      <c r="D11" s="75"/>
+      <c r="E11" s="75"/>
+      <c r="F11" s="75"/>
+      <c r="G11" s="75">
+        <v>3.77</v>
+      </c>
+      <c r="H11" s="75">
+        <v>2.96</v>
+      </c>
+      <c r="I11" s="75">
+        <v>2.81</v>
+      </c>
+      <c r="J11" s="75">
+        <v>2.87</v>
+      </c>
+      <c r="K11" s="75">
+        <v>2.77</v>
+      </c>
+      <c r="L11" s="75">
+        <v>2.78</v>
       </c>
       <c r="M11" s="16">
-        <v>0.98593799999999998</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
@@ -2678,32 +2700,32 @@
         <v>22</v>
       </c>
       <c r="B12" s="54"/>
-      <c r="C12" s="53"/>
-      <c r="D12" s="53"/>
-      <c r="E12" s="53">
-        <v>2.9476800000000001</v>
-      </c>
-      <c r="F12" s="53">
-        <v>1.4350700000000001</v>
-      </c>
-      <c r="G12" s="53"/>
-      <c r="H12" s="53">
-        <v>3.9874900000000002</v>
-      </c>
-      <c r="I12" s="53">
-        <v>4.8409000000000004</v>
-      </c>
-      <c r="J12" s="53">
-        <v>1.5617700000000001</v>
-      </c>
-      <c r="K12" s="53">
-        <v>1.57603</v>
-      </c>
-      <c r="L12" s="53">
-        <v>4.5525200000000003</v>
+      <c r="C12" s="75"/>
+      <c r="D12" s="75"/>
+      <c r="E12" s="75">
+        <v>39.630000000000003</v>
+      </c>
+      <c r="F12" s="75">
+        <v>38</v>
+      </c>
+      <c r="G12" s="70"/>
+      <c r="H12" s="75">
+        <v>35.81</v>
+      </c>
+      <c r="I12" s="75">
+        <v>36.65</v>
+      </c>
+      <c r="J12" s="75">
+        <v>36.700000000000003</v>
+      </c>
+      <c r="K12" s="75">
+        <v>35.39</v>
+      </c>
+      <c r="L12" s="75">
+        <v>36.81</v>
       </c>
       <c r="M12" s="16">
-        <v>2.4393500000000001</v>
+        <v>36.770000000000003</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -2713,30 +2735,30 @@
       <c r="B13" s="55"/>
       <c r="C13" s="17"/>
       <c r="D13" s="17">
-        <v>44.9589</v>
-      </c>
-      <c r="E13" s="17"/>
+        <v>257.83999999999997</v>
+      </c>
+      <c r="E13" s="76"/>
       <c r="F13" s="17">
-        <v>122.503</v>
-      </c>
-      <c r="G13" s="17"/>
+        <v>241.63</v>
+      </c>
+      <c r="G13" s="76"/>
       <c r="H13" s="17">
-        <v>142.24299999999999</v>
+        <v>284.51</v>
       </c>
       <c r="I13" s="17">
-        <v>124.967</v>
+        <v>316.27</v>
       </c>
       <c r="J13" s="17">
-        <v>211.232</v>
+        <v>243.47</v>
       </c>
       <c r="K13" s="17">
-        <v>185.357</v>
+        <v>295.52999999999997</v>
       </c>
       <c r="L13" s="17">
-        <v>229.922</v>
+        <v>277.05</v>
       </c>
       <c r="M13" s="18">
-        <v>140.16499999999999</v>
+        <v>271.58999999999997</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -2745,7 +2767,7 @@
         <v>19</v>
       </c>
       <c r="B15" s="64" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C15" s="61"/>
       <c r="D15" s="61"/>
@@ -2803,34 +2825,34 @@
         <v>20</v>
       </c>
       <c r="B17" s="56">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="C17" s="57">
         <v>0</v>
       </c>
-      <c r="D17" s="58"/>
-      <c r="E17" s="58"/>
-      <c r="F17" s="57">
-        <v>0</v>
-      </c>
-      <c r="G17" s="58"/>
-      <c r="H17" s="57">
-        <v>0.03</v>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="58">
+        <v>0</v>
+      </c>
+      <c r="G17" s="70"/>
+      <c r="H17" s="58">
+        <v>0</v>
       </c>
       <c r="I17" s="57">
         <v>0</v>
       </c>
-      <c r="J17" s="57">
-        <v>0.7</v>
+      <c r="J17" s="58">
+        <v>0.23</v>
       </c>
       <c r="K17" s="57">
-        <v>1.69</v>
+        <v>1.36</v>
       </c>
       <c r="L17" s="57">
-        <v>3.04</v>
+        <v>2.4700000000000002</v>
       </c>
       <c r="M17" s="59">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
@@ -2838,30 +2860,30 @@
         <v>21</v>
       </c>
       <c r="B18" s="54"/>
-      <c r="C18" s="53"/>
-      <c r="D18" s="53"/>
-      <c r="E18" s="53"/>
-      <c r="F18" s="53"/>
-      <c r="G18" s="2">
-        <v>0</v>
-      </c>
-      <c r="H18" s="2">
-        <v>0.03</v>
-      </c>
-      <c r="I18" s="2">
-        <v>0.61</v>
-      </c>
-      <c r="J18" s="2">
-        <v>1.81</v>
-      </c>
-      <c r="K18" s="2">
-        <v>2.86</v>
-      </c>
-      <c r="L18" s="2">
-        <v>4.2300000000000004</v>
+      <c r="C18" s="75"/>
+      <c r="D18" s="75"/>
+      <c r="E18" s="75"/>
+      <c r="F18" s="75"/>
+      <c r="G18" s="72">
+        <v>0</v>
+      </c>
+      <c r="H18" s="72">
+        <v>0</v>
+      </c>
+      <c r="I18" s="72">
+        <v>0.31</v>
+      </c>
+      <c r="J18" s="72">
+        <v>1.46</v>
+      </c>
+      <c r="K18" s="72">
+        <v>2.58</v>
+      </c>
+      <c r="L18" s="72">
+        <v>3.67</v>
       </c>
       <c r="M18" s="29">
-        <v>5.0199999999999996</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
@@ -2869,32 +2891,32 @@
         <v>22</v>
       </c>
       <c r="B19" s="54"/>
-      <c r="C19" s="53"/>
-      <c r="D19" s="53"/>
-      <c r="E19" s="2">
-        <v>0</v>
-      </c>
-      <c r="F19" s="2">
-        <v>0</v>
-      </c>
-      <c r="G19" s="53"/>
-      <c r="H19" s="2">
-        <v>0.84</v>
-      </c>
-      <c r="I19" s="2">
-        <v>1.99</v>
-      </c>
-      <c r="J19" s="2">
-        <v>3.11</v>
-      </c>
-      <c r="K19" s="2">
-        <v>4.21</v>
-      </c>
-      <c r="L19" s="2">
-        <v>5.29</v>
+      <c r="C19" s="75"/>
+      <c r="D19" s="75"/>
+      <c r="E19" s="72">
+        <v>0</v>
+      </c>
+      <c r="F19" s="72">
+        <v>0</v>
+      </c>
+      <c r="G19" s="70"/>
+      <c r="H19" s="75">
+        <v>1.06</v>
+      </c>
+      <c r="I19" s="72">
+        <v>2.21</v>
+      </c>
+      <c r="J19" s="72">
+        <v>3.34</v>
+      </c>
+      <c r="K19" s="72">
+        <v>4.4400000000000004</v>
+      </c>
+      <c r="L19" s="72">
+        <v>5.51</v>
       </c>
       <c r="M19" s="29">
-        <v>6.34</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -2906,11 +2928,11 @@
       <c r="D20" s="17">
         <v>0</v>
       </c>
-      <c r="E20" s="17"/>
+      <c r="E20" s="76"/>
       <c r="F20" s="17">
         <v>0</v>
       </c>
-      <c r="G20" s="17"/>
+      <c r="G20" s="76"/>
       <c r="H20" s="17">
         <v>0</v>
       </c>
@@ -2924,10 +2946,10 @@
         <v>0</v>
       </c>
       <c r="L20" s="17">
-        <v>1.07</v>
+        <v>0.42</v>
       </c>
       <c r="M20" s="18">
-        <v>2.0099999999999998</v>
+        <v>1.53</v>
       </c>
     </row>
   </sheetData>
@@ -2958,7 +2980,7 @@
         <v>19</v>
       </c>
       <c r="B1" s="64" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="C1" s="61"/>
       <c r="D1" s="61"/>
@@ -3012,37 +3034,37 @@
         <v>20</v>
       </c>
       <c r="B3" s="52">
-        <v>-1.54</v>
+        <v>-2.2907500000000001</v>
       </c>
       <c r="C3" s="53">
-        <v>-2.7743799999999998</v>
+        <v>-4.1074200000000003</v>
       </c>
       <c r="D3" s="53">
-        <v>-4.0891299999999999</v>
+        <v>-5.4601600000000001</v>
       </c>
       <c r="E3" s="53">
-        <v>-5.3314199999999996</v>
+        <v>-6.7148099999999999</v>
       </c>
       <c r="F3" s="53">
-        <v>-6.4863299999999997</v>
+        <v>-7.8564600000000002</v>
       </c>
       <c r="G3" s="53">
-        <v>-7.2667200000000003</v>
+        <v>-8.4760200000000001</v>
       </c>
       <c r="H3" s="53">
-        <v>-7.4532600000000002</v>
+        <v>-8.6761900000000001</v>
       </c>
       <c r="I3" s="53">
-        <v>-7.5927499999999997</v>
+        <v>-8.87331</v>
       </c>
       <c r="J3" s="53">
-        <v>-7.7242300000000004</v>
+        <v>-9.0272299999999994</v>
       </c>
       <c r="K3" s="53">
-        <v>-7.6716800000000003</v>
+        <v>-9.0822900000000004</v>
       </c>
       <c r="L3" s="16">
-        <v>-7.8611300000000002</v>
+        <v>-9.1313099999999991</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
@@ -3050,37 +3072,37 @@
         <v>21</v>
       </c>
       <c r="B4" s="54">
-        <v>-1.17</v>
+        <v>-1.25518</v>
       </c>
       <c r="C4" s="53">
-        <v>-1.5385</v>
+        <v>-1.63361</v>
       </c>
       <c r="D4" s="53">
-        <v>-1.8991199999999999</v>
+        <v>-2.00048</v>
       </c>
       <c r="E4" s="53">
-        <v>-2.2501199999999999</v>
+        <v>-2.35955</v>
       </c>
       <c r="F4" s="53">
-        <v>-2.5049199999999998</v>
+        <v>-2.71319</v>
       </c>
       <c r="G4" s="53">
-        <v>-2.9354399999999998</v>
+        <v>-3.0620699999999998</v>
       </c>
       <c r="H4" s="53">
-        <v>-3.2768999999999999</v>
+        <v>-3.4085399999999999</v>
       </c>
       <c r="I4" s="53">
-        <v>-3.5948899999999999</v>
+        <v>-3.7523499999999999</v>
       </c>
       <c r="J4" s="53">
-        <v>-3.9493100000000001</v>
+        <v>-4.08805</v>
       </c>
       <c r="K4" s="53">
-        <v>-4.2320000000000002</v>
+        <v>-4.4092099999999999</v>
       </c>
       <c r="L4" s="16">
-        <v>-4.5682099999999997</v>
+        <v>-4.7075399999999998</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
@@ -3088,37 +3110,37 @@
         <v>22</v>
       </c>
       <c r="B5" s="54">
-        <v>-2.0699999999999998</v>
+        <v>-1.2844100000000001</v>
       </c>
       <c r="C5" s="53">
-        <v>-2.41865</v>
+        <v>-1.7714700000000001</v>
       </c>
       <c r="D5" s="53">
-        <v>-2.9945400000000002</v>
+        <v>-2.1694800000000001</v>
       </c>
       <c r="E5" s="53">
-        <v>-3.4371100000000001</v>
+        <v>-2.55829</v>
       </c>
       <c r="F5" s="53">
-        <v>-3.81047</v>
+        <v>-2.9446599999999998</v>
       </c>
       <c r="G5" s="53">
-        <v>-4.2753800000000002</v>
+        <v>-3.3252000000000002</v>
       </c>
       <c r="H5" s="53">
-        <v>-4.68377</v>
+        <v>-3.7014499999999999</v>
       </c>
       <c r="I5" s="53">
-        <v>-5.09999</v>
+        <v>-4.0714399999999999</v>
       </c>
       <c r="J5" s="53">
-        <v>-5.5037000000000003</v>
+        <v>-4.4296600000000002</v>
       </c>
       <c r="K5" s="53">
-        <v>-5.7949999999999999</v>
+        <v>-4.7069799999999997</v>
       </c>
       <c r="L5" s="16">
-        <v>-6.1381699999999997</v>
+        <v>-4.9765100000000002</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -3126,37 +3148,37 @@
         <v>23</v>
       </c>
       <c r="B6" s="55">
-        <v>-2.77</v>
+        <v>-2.8877600000000001</v>
       </c>
       <c r="C6" s="17">
-        <v>-3.7648999999999999</v>
+        <v>-4.4904099999999998</v>
       </c>
       <c r="D6" s="17">
-        <v>-5.5349899999999996</v>
+        <v>-5.8090000000000002</v>
       </c>
       <c r="E6" s="17">
-        <v>-6.2359</v>
+        <v>-6.7631100000000002</v>
       </c>
       <c r="F6" s="17">
-        <v>-7.2943199999999999</v>
+        <v>-7.46523</v>
       </c>
       <c r="G6" s="17">
-        <v>-7.6234900000000003</v>
+        <v>-8.1290999999999993</v>
       </c>
       <c r="H6" s="17">
-        <v>-8.6134400000000007</v>
+        <v>-8.7678200000000004</v>
       </c>
       <c r="I6" s="17">
-        <v>-8.81067</v>
+        <v>-9.3747900000000008</v>
       </c>
       <c r="J6" s="17">
-        <v>-9.7289399999999997</v>
+        <v>-9.8490000000000002</v>
       </c>
       <c r="K6" s="17">
-        <v>-9.7181300000000004</v>
+        <v>-10.2202</v>
       </c>
       <c r="L6" s="18">
-        <v>-10.128500000000001</v>
+        <v>-10.5829</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -3219,37 +3241,37 @@
         <v>20</v>
       </c>
       <c r="B10" s="52">
-        <v>3.11</v>
+        <v>73.56</v>
       </c>
       <c r="C10" s="53">
-        <v>3.66093</v>
+        <v>100.98</v>
       </c>
       <c r="D10" s="53">
-        <v>3.81359</v>
+        <v>108.38</v>
       </c>
       <c r="E10" s="53">
-        <v>2.4962399999999998</v>
+        <v>115.88</v>
       </c>
       <c r="F10" s="53">
-        <v>8.4510100000000001</v>
+        <v>74.31</v>
       </c>
       <c r="G10" s="53">
-        <v>2.3244699999999998</v>
+        <v>115.95</v>
       </c>
       <c r="H10" s="53">
-        <v>2.8733300000000002</v>
+        <v>70.849999999999994</v>
       </c>
       <c r="I10" s="53">
-        <v>2.0161899999999999</v>
+        <v>119.96</v>
       </c>
       <c r="J10" s="53">
-        <v>1.97529</v>
+        <v>99.94</v>
       </c>
       <c r="K10" s="53">
-        <v>1.7171099999999999</v>
+        <v>107.17</v>
       </c>
       <c r="L10" s="16">
-        <v>1.85301</v>
+        <v>109.78</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
@@ -3257,37 +3279,37 @@
         <v>21</v>
       </c>
       <c r="B11" s="54">
-        <v>0.93</v>
+        <v>3.87</v>
       </c>
       <c r="C11" s="53">
-        <v>1.08138</v>
+        <v>59.72</v>
       </c>
       <c r="D11" s="53">
-        <v>0.93869199999999997</v>
+        <v>58.9</v>
       </c>
       <c r="E11" s="53">
-        <v>1.02522</v>
+        <v>59.49</v>
       </c>
       <c r="F11" s="53">
-        <v>0.78205999999999998</v>
+        <v>50.24</v>
       </c>
       <c r="G11" s="53">
-        <v>6.702</v>
+        <v>2.9</v>
       </c>
       <c r="H11" s="53">
-        <v>0.97508899999999998</v>
+        <v>3.35</v>
       </c>
       <c r="I11" s="53">
-        <v>0.89023099999999999</v>
+        <v>3.18</v>
       </c>
       <c r="J11" s="53">
-        <v>0.93936900000000001</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="K11" s="53">
-        <v>0.95467199999999997</v>
+        <v>57.31</v>
       </c>
       <c r="L11" s="16">
-        <v>7.3017000000000003</v>
+        <v>58.75</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
@@ -3295,37 +3317,37 @@
         <v>22</v>
       </c>
       <c r="B12" s="54">
-        <v>2.95</v>
+        <v>39.619999999999997</v>
       </c>
       <c r="C12" s="53">
-        <v>2.4715500000000001</v>
+        <v>62.8</v>
       </c>
       <c r="D12" s="53">
-        <v>1.39836</v>
+        <v>51.63</v>
       </c>
       <c r="E12" s="53">
-        <v>11.0374</v>
+        <v>2.4</v>
       </c>
       <c r="F12" s="53">
-        <v>1.1968099999999999</v>
+        <v>2.54</v>
       </c>
       <c r="G12" s="53">
-        <v>1.4365399999999999</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="H12" s="53">
-        <v>1.22306</v>
+        <v>52.2</v>
       </c>
       <c r="I12" s="53">
-        <v>1.0690999999999999</v>
+        <v>68.02</v>
       </c>
       <c r="J12" s="53">
-        <v>1.0832299999999999</v>
+        <v>62.05</v>
       </c>
       <c r="K12" s="53">
-        <v>1.29739</v>
+        <v>2.85</v>
       </c>
       <c r="L12" s="16">
-        <v>1.1089199999999999</v>
+        <v>2.3199999999999998</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -3333,37 +3355,37 @@
         <v>23</v>
       </c>
       <c r="B13" s="55">
-        <v>44.96</v>
+        <v>257.24</v>
       </c>
       <c r="C13" s="17">
-        <v>98.632199999999997</v>
+        <v>305.93</v>
       </c>
       <c r="D13" s="17">
-        <v>45.2151</v>
+        <v>271.48</v>
       </c>
       <c r="E13" s="17">
-        <v>77.741200000000006</v>
+        <v>335.65</v>
       </c>
       <c r="F13" s="17">
-        <v>38.270499999999998</v>
+        <v>354.2</v>
       </c>
       <c r="G13" s="17">
-        <v>55.551200000000001</v>
+        <v>288.52999999999997</v>
       </c>
       <c r="H13" s="17">
-        <v>32.417900000000003</v>
+        <v>441.99</v>
       </c>
       <c r="I13" s="17">
-        <v>59.4375</v>
+        <v>372.59</v>
       </c>
       <c r="J13" s="17">
-        <v>33.046700000000001</v>
+        <v>257.77</v>
       </c>
       <c r="K13" s="17">
-        <v>91.980599999999995</v>
+        <v>389.32</v>
       </c>
       <c r="L13" s="18">
-        <v>47.497399999999999</v>
+        <v>380.28</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -3372,7 +3394,7 @@
         <v>19</v>
       </c>
       <c r="B15" s="64" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C15" s="61"/>
       <c r="D15" s="61"/>
@@ -3427,113 +3449,113 @@
       <c r="A17" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="B17" s="49">
-        <v>0</v>
-      </c>
-      <c r="C17" s="2">
-        <v>0</v>
-      </c>
-      <c r="D17" s="2">
-        <v>0</v>
-      </c>
-      <c r="E17" s="2">
-        <v>0</v>
-      </c>
-      <c r="F17" s="2">
-        <v>0</v>
-      </c>
-      <c r="G17" s="2">
-        <v>0</v>
-      </c>
-      <c r="H17" s="2">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="I17" s="2">
-        <v>0.22</v>
-      </c>
-      <c r="J17" s="2">
-        <v>0.01</v>
-      </c>
-      <c r="K17" s="2">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L17" s="29">
-        <v>9</v>
+      <c r="B17" s="67">
+        <v>0</v>
+      </c>
+      <c r="C17" s="70">
+        <v>0</v>
+      </c>
+      <c r="D17" s="70">
+        <v>0</v>
+      </c>
+      <c r="E17" s="70">
+        <v>0</v>
+      </c>
+      <c r="F17" s="70">
+        <v>0</v>
+      </c>
+      <c r="G17" s="70">
+        <v>0</v>
+      </c>
+      <c r="H17" s="70">
+        <v>0</v>
+      </c>
+      <c r="I17" s="70">
+        <v>0</v>
+      </c>
+      <c r="J17" s="70">
+        <v>0.1</v>
+      </c>
+      <c r="K17" s="70">
+        <v>5.42</v>
+      </c>
+      <c r="L17" s="71">
+        <v>10.44</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="B18" s="49">
+      <c r="B18" s="68">
+        <v>0</v>
+      </c>
+      <c r="C18" s="70">
         <v>0.01</v>
       </c>
-      <c r="C18" s="2">
-        <v>0.02</v>
-      </c>
-      <c r="D18" s="2">
-        <v>0.02</v>
-      </c>
-      <c r="E18" s="2">
-        <v>0.01</v>
-      </c>
-      <c r="F18" s="2">
-        <v>0.01</v>
-      </c>
-      <c r="G18" s="2">
-        <v>0</v>
-      </c>
-      <c r="H18" s="2">
-        <v>0</v>
-      </c>
-      <c r="I18" s="2">
-        <v>0</v>
-      </c>
-      <c r="J18" s="2">
-        <v>0.41</v>
-      </c>
-      <c r="K18" s="2">
-        <v>0.03</v>
-      </c>
-      <c r="L18" s="29">
-        <v>0.01</v>
+      <c r="D18" s="70">
+        <v>0</v>
+      </c>
+      <c r="E18" s="70">
+        <v>0</v>
+      </c>
+      <c r="F18" s="70">
+        <v>0</v>
+      </c>
+      <c r="G18" s="70">
+        <v>0</v>
+      </c>
+      <c r="H18" s="70">
+        <v>0</v>
+      </c>
+      <c r="I18" s="70">
+        <v>0</v>
+      </c>
+      <c r="J18" s="70">
+        <v>0</v>
+      </c>
+      <c r="K18" s="70">
+        <v>0</v>
+      </c>
+      <c r="L18" s="71">
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="B19" s="49">
-        <v>100</v>
-      </c>
-      <c r="C19" s="2">
-        <v>100</v>
-      </c>
-      <c r="D19" s="2">
-        <v>100</v>
-      </c>
-      <c r="E19" s="2">
-        <v>100</v>
-      </c>
-      <c r="F19" s="2">
-        <v>100</v>
-      </c>
-      <c r="G19" s="2">
-        <v>100</v>
-      </c>
-      <c r="H19" s="2">
-        <v>100</v>
-      </c>
-      <c r="I19" s="2">
-        <v>100</v>
-      </c>
-      <c r="J19" s="2">
-        <v>100</v>
-      </c>
-      <c r="K19" s="2">
-        <v>100</v>
-      </c>
-      <c r="L19" s="29">
+      <c r="B19" s="68">
+        <v>0</v>
+      </c>
+      <c r="C19" s="70">
+        <v>0</v>
+      </c>
+      <c r="D19" s="70">
+        <v>0</v>
+      </c>
+      <c r="E19" s="70">
+        <v>0</v>
+      </c>
+      <c r="F19" s="70">
+        <v>100</v>
+      </c>
+      <c r="G19" s="70">
+        <v>0</v>
+      </c>
+      <c r="H19" s="70">
+        <v>25.64</v>
+      </c>
+      <c r="I19" s="70">
+        <v>100</v>
+      </c>
+      <c r="J19" s="70">
+        <v>100</v>
+      </c>
+      <c r="K19" s="70">
+        <v>100</v>
+      </c>
+      <c r="L19" s="71">
         <v>100</v>
       </c>
     </row>
@@ -3541,37 +3563,37 @@
       <c r="A20" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="B20" s="49">
-        <v>0.09</v>
-      </c>
-      <c r="C20" s="2">
-        <v>100</v>
-      </c>
-      <c r="D20" s="2">
-        <v>100</v>
-      </c>
-      <c r="E20" s="2">
-        <v>100</v>
-      </c>
-      <c r="F20" s="2">
-        <v>100</v>
-      </c>
-      <c r="G20" s="2">
-        <v>100</v>
-      </c>
-      <c r="H20" s="2">
-        <v>100</v>
-      </c>
-      <c r="I20" s="2">
-        <v>100</v>
-      </c>
-      <c r="J20" s="2">
-        <v>100</v>
-      </c>
-      <c r="K20" s="2">
-        <v>100</v>
-      </c>
-      <c r="L20" s="29">
+      <c r="B20" s="68">
+        <v>0</v>
+      </c>
+      <c r="C20" s="70">
+        <v>0</v>
+      </c>
+      <c r="D20" s="70">
+        <v>0</v>
+      </c>
+      <c r="E20" s="70">
+        <v>0</v>
+      </c>
+      <c r="F20" s="70">
+        <v>0</v>
+      </c>
+      <c r="G20" s="70">
+        <v>97.22</v>
+      </c>
+      <c r="H20" s="70">
+        <v>100</v>
+      </c>
+      <c r="I20" s="70">
+        <v>100</v>
+      </c>
+      <c r="J20" s="70">
+        <v>100</v>
+      </c>
+      <c r="K20" s="70">
+        <v>100</v>
+      </c>
+      <c r="L20" s="71">
         <v>100</v>
       </c>
     </row>
@@ -3579,75 +3601,75 @@
       <c r="A21" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="B21" s="49">
-        <v>0</v>
-      </c>
-      <c r="C21" s="2">
+      <c r="B21" s="68">
         <v>0.01</v>
       </c>
-      <c r="D21" s="2">
-        <v>0</v>
-      </c>
-      <c r="E21" s="2">
-        <v>0</v>
-      </c>
-      <c r="F21" s="2">
-        <v>0</v>
-      </c>
-      <c r="G21" s="2">
-        <v>0</v>
-      </c>
-      <c r="H21" s="2">
-        <v>0</v>
-      </c>
-      <c r="I21" s="2">
-        <v>0</v>
-      </c>
-      <c r="J21" s="2">
-        <v>0</v>
-      </c>
-      <c r="K21" s="2">
-        <v>0</v>
-      </c>
-      <c r="L21" s="29">
-        <v>0.11</v>
+      <c r="C21" s="70">
+        <v>0.01</v>
+      </c>
+      <c r="D21" s="70">
+        <v>0.01</v>
+      </c>
+      <c r="E21" s="70">
+        <v>0.01</v>
+      </c>
+      <c r="F21" s="70">
+        <v>0.01</v>
+      </c>
+      <c r="G21" s="70">
+        <v>0.01</v>
+      </c>
+      <c r="H21" s="70">
+        <v>100</v>
+      </c>
+      <c r="I21" s="70">
+        <v>100</v>
+      </c>
+      <c r="J21" s="70">
+        <v>100</v>
+      </c>
+      <c r="K21" s="70">
+        <v>100</v>
+      </c>
+      <c r="L21" s="71">
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="49">
-        <v>2.67</v>
-      </c>
-      <c r="C22" s="2">
-        <v>22.35</v>
-      </c>
-      <c r="D22" s="2">
-        <v>45.21</v>
-      </c>
-      <c r="E22" s="2">
-        <v>66.11</v>
-      </c>
-      <c r="F22" s="2">
-        <v>85.27</v>
-      </c>
-      <c r="G22" s="2">
-        <v>100</v>
-      </c>
-      <c r="H22" s="2">
-        <v>100</v>
-      </c>
-      <c r="I22" s="2">
-        <v>99.93</v>
-      </c>
-      <c r="J22" s="2">
-        <v>99.96</v>
-      </c>
-      <c r="K22" s="2">
-        <v>100</v>
-      </c>
-      <c r="L22" s="29">
+      <c r="B22" s="68">
+        <v>1.04</v>
+      </c>
+      <c r="C22" s="70">
+        <v>27.67</v>
+      </c>
+      <c r="D22" s="70">
+        <v>50.02</v>
+      </c>
+      <c r="E22" s="70">
+        <v>70.69</v>
+      </c>
+      <c r="F22" s="70">
+        <v>89.63</v>
+      </c>
+      <c r="G22" s="70">
+        <v>100</v>
+      </c>
+      <c r="H22" s="70">
+        <v>100</v>
+      </c>
+      <c r="I22" s="70">
+        <v>100</v>
+      </c>
+      <c r="J22" s="70">
+        <v>100</v>
+      </c>
+      <c r="K22" s="70">
+        <v>100</v>
+      </c>
+      <c r="L22" s="71">
         <v>100</v>
       </c>
     </row>
@@ -3655,113 +3677,91 @@
       <c r="A23" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="B23" s="49">
-        <v>0</v>
-      </c>
-      <c r="C23" s="2">
-        <v>0</v>
-      </c>
-      <c r="D23" s="2">
-        <v>0</v>
-      </c>
-      <c r="E23" s="2">
-        <v>0</v>
-      </c>
-      <c r="F23" s="2">
-        <v>0</v>
-      </c>
-      <c r="G23" s="2">
-        <v>3.38</v>
-      </c>
-      <c r="H23" s="2">
-        <v>23.28</v>
-      </c>
-      <c r="I23" s="2">
-        <v>41.39</v>
-      </c>
-      <c r="J23" s="2">
-        <v>58.94</v>
-      </c>
-      <c r="K23" s="2">
-        <v>62.53</v>
-      </c>
-      <c r="L23" s="29">
-        <v>63.92</v>
+      <c r="B23" s="69">
+        <v>0</v>
+      </c>
+      <c r="C23" s="70">
+        <v>0</v>
+      </c>
+      <c r="D23" s="70">
+        <v>0</v>
+      </c>
+      <c r="E23" s="70">
+        <v>0</v>
+      </c>
+      <c r="F23" s="70">
+        <v>0</v>
+      </c>
+      <c r="G23" s="70">
+        <v>8.68</v>
+      </c>
+      <c r="H23" s="70">
+        <v>28.47</v>
+      </c>
+      <c r="I23" s="70">
+        <v>46.79</v>
+      </c>
+      <c r="J23" s="70">
+        <v>63.52</v>
+      </c>
+      <c r="K23" s="70">
+        <v>64.930000000000007</v>
+      </c>
+      <c r="L23" s="71">
+        <v>66.09</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="B24" s="43">
-        <v>1</v>
-      </c>
-      <c r="C24" s="44">
-        <v>1.05</v>
-      </c>
-      <c r="D24" s="44">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="E24" s="44">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="F24" s="44">
-        <v>1.2</v>
-      </c>
-      <c r="G24" s="44">
-        <v>1.25</v>
-      </c>
-      <c r="H24" s="44">
-        <v>1.3</v>
-      </c>
-      <c r="I24" s="44">
-        <v>1.35</v>
-      </c>
-      <c r="J24" s="44">
-        <v>1.4</v>
-      </c>
-      <c r="K24" s="44">
-        <v>1.45</v>
-      </c>
-      <c r="L24" s="45">
-        <v>1.5</v>
-      </c>
+      <c r="B24" s="43"/>
+      <c r="C24" s="44"/>
+      <c r="D24" s="44"/>
+      <c r="E24" s="44"/>
+      <c r="F24" s="44"/>
+      <c r="G24" s="44"/>
+      <c r="H24" s="44"/>
+      <c r="I24" s="44"/>
+      <c r="J24" s="44"/>
+      <c r="K24" s="44"/>
+      <c r="L24" s="45"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="B25" s="49">
-        <v>0</v>
-      </c>
-      <c r="C25" s="2">
-        <v>0</v>
-      </c>
-      <c r="D25" s="2">
-        <v>0</v>
-      </c>
-      <c r="E25" s="2">
-        <v>0</v>
-      </c>
-      <c r="F25" s="2">
-        <v>0</v>
-      </c>
-      <c r="G25" s="2">
-        <v>0</v>
-      </c>
-      <c r="H25" s="2">
-        <v>0</v>
-      </c>
-      <c r="I25" s="2">
-        <v>0</v>
-      </c>
-      <c r="J25" s="2">
-        <v>0</v>
-      </c>
-      <c r="K25" s="2">
-        <v>0</v>
-      </c>
-      <c r="L25" s="29">
+      <c r="B25" s="67">
+        <v>0</v>
+      </c>
+      <c r="C25" s="70">
+        <v>0</v>
+      </c>
+      <c r="D25" s="70">
+        <v>0</v>
+      </c>
+      <c r="E25" s="70">
+        <v>0</v>
+      </c>
+      <c r="F25" s="70">
+        <v>0</v>
+      </c>
+      <c r="G25" s="70">
+        <v>0</v>
+      </c>
+      <c r="H25" s="70">
+        <v>0</v>
+      </c>
+      <c r="I25" s="70">
+        <v>0</v>
+      </c>
+      <c r="J25" s="70">
+        <v>0</v>
+      </c>
+      <c r="K25" s="70">
+        <v>0</v>
+      </c>
+      <c r="L25" s="71">
         <v>0</v>
       </c>
     </row>
@@ -3769,81 +3769,81 @@
       <c r="A26" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="B26" s="49">
-        <v>0</v>
-      </c>
-      <c r="C26" s="2">
-        <v>17.03</v>
-      </c>
-      <c r="D26" s="2">
-        <v>27.41</v>
-      </c>
-      <c r="E26" s="2">
-        <v>28.86</v>
-      </c>
-      <c r="F26" s="2">
-        <v>29.17</v>
-      </c>
-      <c r="G26" s="2">
-        <v>34.340000000000003</v>
-      </c>
-      <c r="H26" s="2">
-        <v>30.69</v>
-      </c>
-      <c r="I26" s="2">
-        <v>38.81</v>
-      </c>
-      <c r="J26" s="2">
-        <v>36.18</v>
-      </c>
-      <c r="K26" s="2">
-        <v>37.18</v>
-      </c>
-      <c r="L26" s="29">
-        <v>38.81</v>
+      <c r="B26" s="68">
+        <v>19.95</v>
+      </c>
+      <c r="C26" s="70">
+        <v>32.04</v>
+      </c>
+      <c r="D26" s="70">
+        <v>40</v>
+      </c>
+      <c r="E26" s="70">
+        <v>40.76</v>
+      </c>
+      <c r="F26" s="70">
+        <v>35.130000000000003</v>
+      </c>
+      <c r="G26" s="70">
+        <v>38.380000000000003</v>
+      </c>
+      <c r="H26" s="70">
+        <v>39.72</v>
+      </c>
+      <c r="I26" s="70">
+        <v>41.15</v>
+      </c>
+      <c r="J26" s="70">
+        <v>42.33</v>
+      </c>
+      <c r="K26" s="70">
+        <v>42.34</v>
+      </c>
+      <c r="L26" s="71">
+        <v>47.45</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="B27" s="49">
-        <v>4.3600000000000003</v>
-      </c>
-      <c r="C27" s="2">
-        <v>8.56</v>
-      </c>
-      <c r="D27" s="2">
-        <v>15.36</v>
-      </c>
-      <c r="E27" s="2">
-        <v>23.33</v>
-      </c>
-      <c r="F27" s="2">
-        <v>30.69</v>
-      </c>
-      <c r="G27" s="2">
-        <v>36.700000000000003</v>
-      </c>
-      <c r="H27" s="2">
-        <v>43.95</v>
-      </c>
-      <c r="I27" s="2">
-        <v>48.12</v>
-      </c>
-      <c r="J27" s="2">
-        <v>54.27</v>
-      </c>
-      <c r="K27" s="2">
-        <v>59.16</v>
-      </c>
-      <c r="L27" s="29">
-        <v>63.67</v>
+      <c r="B27" s="69">
+        <v>0</v>
+      </c>
+      <c r="C27" s="70">
+        <v>7.24</v>
+      </c>
+      <c r="D27" s="70">
+        <v>14.49</v>
+      </c>
+      <c r="E27" s="70">
+        <v>22.52</v>
+      </c>
+      <c r="F27" s="70">
+        <v>31.27</v>
+      </c>
+      <c r="G27" s="70">
+        <v>37.479999999999997</v>
+      </c>
+      <c r="H27" s="70">
+        <v>43.57</v>
+      </c>
+      <c r="I27" s="70">
+        <v>49.17</v>
+      </c>
+      <c r="J27" s="70">
+        <v>54.4</v>
+      </c>
+      <c r="K27" s="70">
+        <v>59.51</v>
+      </c>
+      <c r="L27" s="71">
+        <v>63.16</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="51" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B28" s="43">
         <v>1</v>
@@ -3886,35 +3886,35 @@
       <c r="B29" s="49">
         <v>0</v>
       </c>
-      <c r="C29" s="2">
-        <v>0</v>
-      </c>
-      <c r="D29" s="2">
-        <v>0.01</v>
-      </c>
-      <c r="E29" s="2">
-        <v>0</v>
-      </c>
-      <c r="F29" s="2">
-        <v>0</v>
-      </c>
-      <c r="G29" s="2">
-        <v>0.01</v>
-      </c>
-      <c r="H29" s="2">
-        <v>0.01</v>
-      </c>
-      <c r="I29" s="2">
-        <v>0</v>
-      </c>
-      <c r="J29" s="2">
-        <v>0</v>
-      </c>
-      <c r="K29" s="2">
-        <v>0.02</v>
+      <c r="C29" s="72">
+        <v>0</v>
+      </c>
+      <c r="D29" s="72">
+        <v>0</v>
+      </c>
+      <c r="E29" s="72">
+        <v>0</v>
+      </c>
+      <c r="F29" s="72">
+        <v>0</v>
+      </c>
+      <c r="G29" s="72">
+        <v>0</v>
+      </c>
+      <c r="H29" s="72">
+        <v>0</v>
+      </c>
+      <c r="I29" s="72">
+        <v>0</v>
+      </c>
+      <c r="J29" s="72">
+        <v>0</v>
+      </c>
+      <c r="K29" s="72">
+        <v>0</v>
       </c>
       <c r="L29" s="29">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
@@ -3922,37 +3922,37 @@
         <v>1</v>
       </c>
       <c r="B30" s="49">
-        <v>0.01</v>
-      </c>
-      <c r="C30" s="2">
-        <v>0</v>
-      </c>
-      <c r="D30" s="2">
-        <v>0.01</v>
-      </c>
-      <c r="E30" s="2">
-        <v>0</v>
-      </c>
-      <c r="F30" s="2">
-        <v>0</v>
-      </c>
-      <c r="G30" s="2">
-        <v>0.01</v>
-      </c>
-      <c r="H30" s="2">
-        <v>0.01</v>
-      </c>
-      <c r="I30" s="2">
-        <v>0</v>
-      </c>
-      <c r="J30" s="2">
-        <v>0</v>
-      </c>
-      <c r="K30" s="2">
+        <v>0</v>
+      </c>
+      <c r="C30" s="72">
+        <v>0</v>
+      </c>
+      <c r="D30" s="72">
+        <v>0</v>
+      </c>
+      <c r="E30" s="72">
+        <v>0</v>
+      </c>
+      <c r="F30" s="72">
+        <v>0</v>
+      </c>
+      <c r="G30" s="72">
+        <v>0</v>
+      </c>
+      <c r="H30" s="72">
+        <v>0</v>
+      </c>
+      <c r="I30" s="72">
+        <v>0</v>
+      </c>
+      <c r="J30" s="72">
+        <v>0</v>
+      </c>
+      <c r="K30" s="72">
         <v>0</v>
       </c>
       <c r="L30" s="29">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
@@ -3962,32 +3962,32 @@
       <c r="B31" s="49">
         <v>0</v>
       </c>
-      <c r="C31" s="2">
-        <v>19.78</v>
-      </c>
-      <c r="D31" s="2">
-        <v>40.4</v>
-      </c>
-      <c r="E31" s="2">
-        <v>53.24</v>
-      </c>
-      <c r="F31" s="2">
-        <v>64.900000000000006</v>
-      </c>
-      <c r="G31" s="2">
-        <v>75.19</v>
-      </c>
-      <c r="H31" s="2">
-        <v>85.16</v>
-      </c>
-      <c r="I31" s="2">
-        <v>94.21</v>
-      </c>
-      <c r="J31" s="2">
-        <v>100</v>
-      </c>
-      <c r="K31" s="2">
-        <v>99.92</v>
+      <c r="C31" s="72">
+        <v>0</v>
+      </c>
+      <c r="D31" s="72">
+        <v>39.340000000000003</v>
+      </c>
+      <c r="E31" s="72">
+        <v>51.9</v>
+      </c>
+      <c r="F31" s="72">
+        <v>63.43</v>
+      </c>
+      <c r="G31" s="72">
+        <v>73.849999999999994</v>
+      </c>
+      <c r="H31" s="72">
+        <v>83.64</v>
+      </c>
+      <c r="I31" s="72">
+        <v>92.69</v>
+      </c>
+      <c r="J31" s="72">
+        <v>99.87</v>
+      </c>
+      <c r="K31" s="72">
+        <v>99.99</v>
       </c>
       <c r="L31" s="29">
         <v>100</v>
@@ -4000,35 +4000,35 @@
       <c r="B32" s="49">
         <v>0</v>
       </c>
-      <c r="C32" s="2">
-        <v>0</v>
-      </c>
-      <c r="D32" s="2">
-        <v>0</v>
-      </c>
-      <c r="E32" s="2">
-        <v>0</v>
-      </c>
-      <c r="F32" s="2">
-        <v>0</v>
-      </c>
-      <c r="G32" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="H32" s="2">
-        <v>0</v>
-      </c>
-      <c r="I32" s="2">
-        <v>0</v>
-      </c>
-      <c r="J32" s="2">
-        <v>0.18</v>
-      </c>
-      <c r="K32" s="2">
-        <v>4.2699999999999996</v>
+      <c r="C32" s="72">
+        <v>0</v>
+      </c>
+      <c r="D32" s="72">
+        <v>0</v>
+      </c>
+      <c r="E32" s="72">
+        <v>0</v>
+      </c>
+      <c r="F32" s="72">
+        <v>0</v>
+      </c>
+      <c r="G32" s="72">
+        <v>0</v>
+      </c>
+      <c r="H32" s="72">
+        <v>0</v>
+      </c>
+      <c r="I32" s="72">
+        <v>0</v>
+      </c>
+      <c r="J32" s="72">
+        <v>0</v>
+      </c>
+      <c r="K32" s="72">
+        <v>0</v>
       </c>
       <c r="L32" s="29">
-        <v>8.39</v>
+        <v>3.86</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
@@ -4038,35 +4038,35 @@
       <c r="B33" s="49">
         <v>0</v>
       </c>
-      <c r="C33" s="2">
-        <v>3.07</v>
-      </c>
-      <c r="D33" s="2">
-        <v>10.220000000000001</v>
-      </c>
-      <c r="E33" s="2">
-        <v>20.3</v>
-      </c>
-      <c r="F33" s="2">
-        <v>29.4</v>
-      </c>
-      <c r="G33" s="2">
-        <v>38.19</v>
-      </c>
-      <c r="H33" s="2">
-        <v>46.2</v>
-      </c>
-      <c r="I33" s="2">
-        <v>53.58</v>
-      </c>
-      <c r="J33" s="2">
-        <v>61.95</v>
-      </c>
-      <c r="K33" s="2">
-        <v>65.59</v>
+      <c r="C33" s="72">
+        <v>0</v>
+      </c>
+      <c r="D33" s="72">
+        <v>0</v>
+      </c>
+      <c r="E33" s="72">
+        <v>0</v>
+      </c>
+      <c r="F33" s="72">
+        <v>34.47</v>
+      </c>
+      <c r="G33" s="72">
+        <v>43.08</v>
+      </c>
+      <c r="H33" s="72">
+        <v>50.92</v>
+      </c>
+      <c r="I33" s="72">
+        <v>58.17</v>
+      </c>
+      <c r="J33" s="72">
+        <v>65.760000000000005</v>
+      </c>
+      <c r="K33" s="72">
+        <v>77.25</v>
       </c>
       <c r="L33" s="29">
-        <v>68.41</v>
+        <v>80.459999999999994</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
@@ -4074,33 +4074,33 @@
         <v>15</v>
       </c>
       <c r="B34" s="49">
-        <v>19.2</v>
-      </c>
-      <c r="C34" s="2">
-        <v>99.29</v>
-      </c>
-      <c r="D34" s="2">
-        <v>99.39</v>
-      </c>
-      <c r="E34" s="2">
-        <v>100</v>
-      </c>
-      <c r="F34" s="2">
-        <v>99.37</v>
-      </c>
-      <c r="G34" s="2">
-        <v>100</v>
-      </c>
-      <c r="H34" s="2">
-        <v>99.25</v>
-      </c>
-      <c r="I34" s="2">
-        <v>100</v>
-      </c>
-      <c r="J34" s="2">
-        <v>100</v>
-      </c>
-      <c r="K34" s="2">
+        <v>19.55</v>
+      </c>
+      <c r="C34" s="72">
+        <v>100</v>
+      </c>
+      <c r="D34" s="72">
+        <v>100</v>
+      </c>
+      <c r="E34" s="72">
+        <v>100</v>
+      </c>
+      <c r="F34" s="72">
+        <v>100</v>
+      </c>
+      <c r="G34" s="72">
+        <v>100</v>
+      </c>
+      <c r="H34" s="72">
+        <v>100</v>
+      </c>
+      <c r="I34" s="72">
+        <v>100</v>
+      </c>
+      <c r="J34" s="72">
+        <v>100</v>
+      </c>
+      <c r="K34" s="72">
         <v>100</v>
       </c>
       <c r="L34" s="29">
@@ -4152,31 +4152,31 @@
       <c r="B36" s="49">
         <v>0</v>
       </c>
-      <c r="C36" s="2">
-        <v>0</v>
-      </c>
-      <c r="D36" s="2">
-        <v>0</v>
-      </c>
-      <c r="E36" s="2">
-        <v>0</v>
-      </c>
-      <c r="F36" s="2">
-        <v>0</v>
-      </c>
-      <c r="G36" s="2">
-        <v>0</v>
-      </c>
-      <c r="H36" s="2">
-        <v>0</v>
-      </c>
-      <c r="I36" s="2">
-        <v>0</v>
-      </c>
-      <c r="J36" s="2">
-        <v>0</v>
-      </c>
-      <c r="K36" s="2">
+      <c r="C36" s="72">
+        <v>0</v>
+      </c>
+      <c r="D36" s="72">
+        <v>0</v>
+      </c>
+      <c r="E36" s="72">
+        <v>0</v>
+      </c>
+      <c r="F36" s="72">
+        <v>0</v>
+      </c>
+      <c r="G36" s="72">
+        <v>0</v>
+      </c>
+      <c r="H36" s="72">
+        <v>0</v>
+      </c>
+      <c r="I36" s="72">
+        <v>0</v>
+      </c>
+      <c r="J36" s="72">
+        <v>0</v>
+      </c>
+      <c r="K36" s="72">
         <v>0</v>
       </c>
       <c r="L36" s="29">
@@ -4190,31 +4190,31 @@
       <c r="B37" s="49">
         <v>0</v>
       </c>
-      <c r="C37" s="2">
-        <v>0</v>
-      </c>
-      <c r="D37" s="2">
-        <v>0</v>
-      </c>
-      <c r="E37" s="2">
-        <v>0</v>
-      </c>
-      <c r="F37" s="2">
-        <v>0</v>
-      </c>
-      <c r="G37" s="2">
-        <v>0</v>
-      </c>
-      <c r="H37" s="2">
-        <v>0</v>
-      </c>
-      <c r="I37" s="2">
-        <v>0</v>
-      </c>
-      <c r="J37" s="2">
-        <v>0</v>
-      </c>
-      <c r="K37" s="2">
+      <c r="C37" s="72">
+        <v>0</v>
+      </c>
+      <c r="D37" s="72">
+        <v>0</v>
+      </c>
+      <c r="E37" s="72">
+        <v>0</v>
+      </c>
+      <c r="F37" s="72">
+        <v>0</v>
+      </c>
+      <c r="G37" s="72">
+        <v>0</v>
+      </c>
+      <c r="H37" s="72">
+        <v>0</v>
+      </c>
+      <c r="I37" s="72">
+        <v>0</v>
+      </c>
+      <c r="J37" s="72">
+        <v>0</v>
+      </c>
+      <c r="K37" s="72">
         <v>0</v>
       </c>
       <c r="L37" s="29">
@@ -4226,37 +4226,37 @@
         <v>2</v>
       </c>
       <c r="B38" s="49">
-        <v>0.04</v>
-      </c>
-      <c r="C38" s="2">
-        <v>0</v>
-      </c>
-      <c r="D38" s="2">
-        <v>53.71</v>
-      </c>
-      <c r="E38" s="2">
-        <v>95.35</v>
-      </c>
-      <c r="F38" s="2">
-        <v>100</v>
-      </c>
-      <c r="G38" s="2">
-        <v>95.62</v>
-      </c>
-      <c r="H38" s="2">
-        <v>100</v>
-      </c>
-      <c r="I38" s="2">
-        <v>97.3</v>
-      </c>
-      <c r="J38" s="2">
-        <v>100</v>
-      </c>
-      <c r="K38" s="2">
-        <v>98.18</v>
+        <v>0.01</v>
+      </c>
+      <c r="C38" s="72">
+        <v>0.01</v>
+      </c>
+      <c r="D38" s="72">
+        <v>72.430000000000007</v>
+      </c>
+      <c r="E38" s="72">
+        <v>100</v>
+      </c>
+      <c r="F38" s="72">
+        <v>100</v>
+      </c>
+      <c r="G38" s="72">
+        <v>100</v>
+      </c>
+      <c r="H38" s="72">
+        <v>100</v>
+      </c>
+      <c r="I38" s="72">
+        <v>100</v>
+      </c>
+      <c r="J38" s="72">
+        <v>100</v>
+      </c>
+      <c r="K38" s="72">
+        <v>100</v>
       </c>
       <c r="L38" s="29">
-        <v>97.63</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.2">
@@ -4264,37 +4264,37 @@
         <v>3</v>
       </c>
       <c r="B39" s="49">
-        <v>0</v>
-      </c>
-      <c r="C39" s="2">
-        <v>0.08</v>
-      </c>
-      <c r="D39" s="2">
-        <v>0</v>
-      </c>
-      <c r="E39" s="2">
         <v>0.01</v>
       </c>
-      <c r="F39" s="2">
-        <v>17.170000000000002</v>
-      </c>
-      <c r="G39" s="2">
-        <v>43.69</v>
-      </c>
-      <c r="H39" s="2">
-        <v>63.18</v>
-      </c>
-      <c r="I39" s="2">
-        <v>85.5</v>
-      </c>
-      <c r="J39" s="2">
-        <v>100</v>
-      </c>
-      <c r="K39" s="2">
-        <v>98.65</v>
+      <c r="C39" s="72">
+        <v>0.01</v>
+      </c>
+      <c r="D39" s="72">
+        <v>0.01</v>
+      </c>
+      <c r="E39" s="72">
+        <v>0</v>
+      </c>
+      <c r="F39" s="72">
+        <v>23.38</v>
+      </c>
+      <c r="G39" s="72">
+        <v>47.18</v>
+      </c>
+      <c r="H39" s="72">
+        <v>69.14</v>
+      </c>
+      <c r="I39" s="72">
+        <v>89.48</v>
+      </c>
+      <c r="J39" s="72">
+        <v>100</v>
+      </c>
+      <c r="K39" s="72">
+        <v>100</v>
       </c>
       <c r="L39" s="29">
-        <v>96.47</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.2">
@@ -4304,35 +4304,35 @@
       <c r="B40" s="49">
         <v>0</v>
       </c>
-      <c r="C40" s="2">
-        <v>0</v>
-      </c>
-      <c r="D40" s="2">
-        <v>0</v>
-      </c>
-      <c r="E40" s="2">
-        <v>0</v>
-      </c>
-      <c r="F40" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="G40" s="2">
-        <v>0</v>
-      </c>
-      <c r="H40" s="2">
-        <v>0.8</v>
-      </c>
-      <c r="I40" s="2">
-        <v>0</v>
-      </c>
-      <c r="J40" s="2">
-        <v>2.17</v>
-      </c>
-      <c r="K40" s="2">
-        <v>33.69</v>
+      <c r="C40" s="72">
+        <v>0</v>
+      </c>
+      <c r="D40" s="72">
+        <v>0</v>
+      </c>
+      <c r="E40" s="72">
+        <v>0</v>
+      </c>
+      <c r="F40" s="72">
+        <v>0</v>
+      </c>
+      <c r="G40" s="72">
+        <v>0</v>
+      </c>
+      <c r="H40" s="72">
+        <v>0</v>
+      </c>
+      <c r="I40" s="72">
+        <v>0</v>
+      </c>
+      <c r="J40" s="72">
+        <v>12.45</v>
+      </c>
+      <c r="K40" s="72">
+        <v>35.75</v>
       </c>
       <c r="L40" s="29">
-        <v>64.87</v>
+        <v>58.53</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.2">
@@ -4340,37 +4340,37 @@
         <v>5</v>
       </c>
       <c r="B41" s="49">
-        <v>100</v>
-      </c>
-      <c r="C41" s="2">
-        <v>100</v>
-      </c>
-      <c r="D41" s="2">
-        <v>100</v>
-      </c>
-      <c r="E41" s="2">
-        <v>100</v>
-      </c>
-      <c r="F41" s="2">
-        <v>100</v>
-      </c>
-      <c r="G41" s="2">
-        <v>100</v>
-      </c>
-      <c r="H41" s="2">
-        <v>100</v>
-      </c>
-      <c r="I41" s="2">
-        <v>97.3</v>
-      </c>
-      <c r="J41" s="2">
-        <v>100</v>
-      </c>
-      <c r="K41" s="2">
-        <v>95.49</v>
+        <v>0</v>
+      </c>
+      <c r="C41" s="72">
+        <v>0</v>
+      </c>
+      <c r="D41" s="72">
+        <v>0</v>
+      </c>
+      <c r="E41" s="72">
+        <v>0</v>
+      </c>
+      <c r="F41" s="72">
+        <v>0</v>
+      </c>
+      <c r="G41" s="72">
+        <v>100</v>
+      </c>
+      <c r="H41" s="72">
+        <v>100</v>
+      </c>
+      <c r="I41" s="72">
+        <v>100</v>
+      </c>
+      <c r="J41" s="72">
+        <v>100</v>
+      </c>
+      <c r="K41" s="72">
+        <v>100</v>
       </c>
       <c r="L41" s="29">
-        <v>48.31</v>
+        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.2">
@@ -4378,37 +4378,37 @@
         <v>6</v>
       </c>
       <c r="B42" s="49">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="C42" s="2">
-        <v>0.43</v>
-      </c>
-      <c r="D42" s="2">
-        <v>0.7</v>
-      </c>
-      <c r="E42" s="2">
-        <v>77.09</v>
-      </c>
-      <c r="F42" s="2">
-        <v>100</v>
-      </c>
-      <c r="G42" s="2">
-        <v>46.35</v>
-      </c>
-      <c r="H42" s="2">
-        <v>100</v>
-      </c>
-      <c r="I42" s="2">
-        <v>69.55</v>
-      </c>
-      <c r="J42" s="2">
-        <v>100</v>
-      </c>
-      <c r="K42" s="2">
-        <v>98.7</v>
+        <v>0</v>
+      </c>
+      <c r="C42" s="72">
+        <v>0</v>
+      </c>
+      <c r="D42" s="72">
+        <v>0</v>
+      </c>
+      <c r="E42" s="72">
+        <v>0</v>
+      </c>
+      <c r="F42" s="72">
+        <v>0</v>
+      </c>
+      <c r="G42" s="72">
+        <v>0</v>
+      </c>
+      <c r="H42" s="72">
+        <v>100</v>
+      </c>
+      <c r="I42" s="72">
+        <v>100</v>
+      </c>
+      <c r="J42" s="72">
+        <v>100</v>
+      </c>
+      <c r="K42" s="72">
+        <v>100</v>
       </c>
       <c r="L42" s="29">
-        <v>30.46</v>
+        <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.2">
@@ -4416,37 +4416,37 @@
         <v>7</v>
       </c>
       <c r="B43" s="49">
-        <v>0.16</v>
-      </c>
-      <c r="C43" s="2">
-        <v>0.04</v>
-      </c>
-      <c r="D43" s="2">
+        <v>0</v>
+      </c>
+      <c r="C43" s="72">
+        <v>0</v>
+      </c>
+      <c r="D43" s="72">
+        <v>0</v>
+      </c>
+      <c r="E43" s="72">
+        <v>0</v>
+      </c>
+      <c r="F43" s="72">
+        <v>0</v>
+      </c>
+      <c r="G43" s="72">
+        <v>0</v>
+      </c>
+      <c r="H43" s="72">
+        <v>0</v>
+      </c>
+      <c r="I43" s="72">
         <v>0.01</v>
       </c>
-      <c r="E43" s="2">
-        <v>0.02</v>
-      </c>
-      <c r="F43" s="2">
-        <v>0.02</v>
-      </c>
-      <c r="G43" s="2">
-        <v>0.04</v>
-      </c>
-      <c r="H43" s="2">
-        <v>0.02</v>
-      </c>
-      <c r="I43" s="2">
-        <v>0.03</v>
-      </c>
-      <c r="J43" s="2">
-        <v>94.34</v>
-      </c>
-      <c r="K43" s="2">
-        <v>70.45</v>
+      <c r="J43" s="72">
+        <v>96.17</v>
+      </c>
+      <c r="K43" s="72">
+        <v>100</v>
       </c>
       <c r="L43" s="29">
-        <v>59.66</v>
+        <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.2">
@@ -4456,35 +4456,35 @@
       <c r="B44" s="49">
         <v>0</v>
       </c>
-      <c r="C44" s="2">
-        <v>0.01</v>
-      </c>
-      <c r="D44" s="2">
-        <v>0.01</v>
-      </c>
-      <c r="E44" s="2">
-        <v>0</v>
-      </c>
-      <c r="F44" s="2">
-        <v>0</v>
-      </c>
-      <c r="G44" s="2">
-        <v>0</v>
-      </c>
-      <c r="H44" s="2">
-        <v>0</v>
-      </c>
-      <c r="I44" s="2">
-        <v>0</v>
-      </c>
-      <c r="J44" s="2">
-        <v>0</v>
-      </c>
-      <c r="K44" s="2">
-        <v>50.42</v>
+      <c r="C44" s="72">
+        <v>0</v>
+      </c>
+      <c r="D44" s="72">
+        <v>0</v>
+      </c>
+      <c r="E44" s="72">
+        <v>0</v>
+      </c>
+      <c r="F44" s="72">
+        <v>0</v>
+      </c>
+      <c r="G44" s="72">
+        <v>0</v>
+      </c>
+      <c r="H44" s="72">
+        <v>0</v>
+      </c>
+      <c r="I44" s="72">
+        <v>0</v>
+      </c>
+      <c r="J44" s="72">
+        <v>0</v>
+      </c>
+      <c r="K44" s="72">
+        <v>53.74</v>
       </c>
       <c r="L44" s="29">
-        <v>80.62</v>
+        <v>99.49</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.2">
@@ -4494,31 +4494,31 @@
       <c r="B45" s="49">
         <v>0</v>
       </c>
-      <c r="C45" s="2">
-        <v>0</v>
-      </c>
-      <c r="D45" s="2">
-        <v>0</v>
-      </c>
-      <c r="E45" s="2">
-        <v>0</v>
-      </c>
-      <c r="F45" s="2">
-        <v>0</v>
-      </c>
-      <c r="G45" s="2">
-        <v>0</v>
-      </c>
-      <c r="H45" s="2">
-        <v>0</v>
-      </c>
-      <c r="I45" s="2">
-        <v>0</v>
-      </c>
-      <c r="J45" s="2">
-        <v>0</v>
-      </c>
-      <c r="K45" s="2">
+      <c r="C45" s="72">
+        <v>0</v>
+      </c>
+      <c r="D45" s="72">
+        <v>0</v>
+      </c>
+      <c r="E45" s="72">
+        <v>0</v>
+      </c>
+      <c r="F45" s="72">
+        <v>0</v>
+      </c>
+      <c r="G45" s="72">
+        <v>0</v>
+      </c>
+      <c r="H45" s="72">
+        <v>0</v>
+      </c>
+      <c r="I45" s="72">
+        <v>0</v>
+      </c>
+      <c r="J45" s="72">
+        <v>0</v>
+      </c>
+      <c r="K45" s="72">
         <v>0</v>
       </c>
       <c r="L45" s="29">
@@ -4532,31 +4532,31 @@
       <c r="B46" s="49">
         <v>0</v>
       </c>
-      <c r="C46" s="2">
-        <v>0</v>
-      </c>
-      <c r="D46" s="2">
-        <v>0</v>
-      </c>
-      <c r="E46" s="2">
-        <v>0</v>
-      </c>
-      <c r="F46" s="2">
-        <v>0</v>
-      </c>
-      <c r="G46" s="2">
-        <v>0</v>
-      </c>
-      <c r="H46" s="2">
-        <v>0</v>
-      </c>
-      <c r="I46" s="2">
-        <v>0</v>
-      </c>
-      <c r="J46" s="2">
-        <v>0</v>
-      </c>
-      <c r="K46" s="2">
+      <c r="C46" s="72">
+        <v>0</v>
+      </c>
+      <c r="D46" s="72">
+        <v>0</v>
+      </c>
+      <c r="E46" s="72">
+        <v>0</v>
+      </c>
+      <c r="F46" s="72">
+        <v>0</v>
+      </c>
+      <c r="G46" s="72">
+        <v>0</v>
+      </c>
+      <c r="H46" s="72">
+        <v>0</v>
+      </c>
+      <c r="I46" s="72">
+        <v>0</v>
+      </c>
+      <c r="J46" s="72">
+        <v>0</v>
+      </c>
+      <c r="K46" s="72">
         <v>0</v>
       </c>
       <c r="L46" s="29">
@@ -4568,37 +4568,37 @@
         <v>11</v>
       </c>
       <c r="B47" s="49">
-        <v>0.2</v>
-      </c>
-      <c r="C47" s="2">
         <v>0.13</v>
       </c>
-      <c r="D47" s="2">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="E47" s="2">
-        <v>0.86</v>
-      </c>
-      <c r="F47" s="2">
-        <v>0.22</v>
-      </c>
-      <c r="G47" s="2">
-        <v>0.21</v>
-      </c>
-      <c r="H47" s="2">
-        <v>0</v>
-      </c>
-      <c r="I47" s="2">
+      <c r="C47" s="72">
+        <v>0.02</v>
+      </c>
+      <c r="D47" s="72">
+        <v>0.19</v>
+      </c>
+      <c r="E47" s="72">
+        <v>0.11</v>
+      </c>
+      <c r="F47" s="72">
+        <v>0.08</v>
+      </c>
+      <c r="G47" s="72">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H47" s="72">
+        <v>0.02</v>
+      </c>
+      <c r="I47" s="72">
         <v>0.09</v>
       </c>
-      <c r="J47" s="2">
-        <v>100</v>
-      </c>
-      <c r="K47" s="2">
-        <v>12.31</v>
+      <c r="J47" s="72">
+        <v>100</v>
+      </c>
+      <c r="K47" s="72">
+        <v>100</v>
       </c>
       <c r="L47" s="29">
-        <v>28.17</v>
+        <v>100</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.2">
@@ -4606,37 +4606,37 @@
         <v>12</v>
       </c>
       <c r="B48" s="49">
-        <v>59.54</v>
-      </c>
-      <c r="C48" s="2">
-        <v>12.07</v>
-      </c>
-      <c r="D48" s="2">
-        <v>100</v>
-      </c>
-      <c r="E48" s="2">
-        <v>76.83</v>
-      </c>
-      <c r="F48" s="2">
-        <v>100</v>
-      </c>
-      <c r="G48" s="2">
-        <v>87.12</v>
-      </c>
-      <c r="H48" s="2">
-        <v>100</v>
-      </c>
-      <c r="I48" s="2">
-        <v>13.48</v>
-      </c>
-      <c r="J48" s="2">
-        <v>100</v>
-      </c>
-      <c r="K48" s="2">
-        <v>43.1</v>
+        <v>100</v>
+      </c>
+      <c r="C48" s="72">
+        <v>100</v>
+      </c>
+      <c r="D48" s="72">
+        <v>100</v>
+      </c>
+      <c r="E48" s="72">
+        <v>100</v>
+      </c>
+      <c r="F48" s="72">
+        <v>100</v>
+      </c>
+      <c r="G48" s="72">
+        <v>100</v>
+      </c>
+      <c r="H48" s="72">
+        <v>100</v>
+      </c>
+      <c r="I48" s="72">
+        <v>100</v>
+      </c>
+      <c r="J48" s="72">
+        <v>100</v>
+      </c>
+      <c r="K48" s="72">
+        <v>100</v>
       </c>
       <c r="L48" s="29">
-        <v>45.81</v>
+        <v>100</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.2">
@@ -4646,35 +4646,35 @@
       <c r="B49" s="49">
         <v>0</v>
       </c>
-      <c r="C49" s="2">
-        <v>0</v>
-      </c>
-      <c r="D49" s="2">
-        <v>0</v>
-      </c>
-      <c r="E49" s="2">
-        <v>72.38</v>
-      </c>
-      <c r="F49" s="2">
-        <v>99.99</v>
-      </c>
-      <c r="G49" s="2">
-        <v>90.58</v>
-      </c>
-      <c r="H49" s="2">
-        <v>100</v>
-      </c>
-      <c r="I49" s="2">
-        <v>91.84</v>
-      </c>
-      <c r="J49" s="2">
-        <v>100</v>
-      </c>
-      <c r="K49" s="2">
-        <v>95.22</v>
+      <c r="C49" s="72">
+        <v>0</v>
+      </c>
+      <c r="D49" s="72">
+        <v>0.01</v>
+      </c>
+      <c r="E49" s="72">
+        <v>90.72</v>
+      </c>
+      <c r="F49" s="72">
+        <v>100</v>
+      </c>
+      <c r="G49" s="72">
+        <v>100</v>
+      </c>
+      <c r="H49" s="72">
+        <v>100</v>
+      </c>
+      <c r="I49" s="72">
+        <v>100</v>
+      </c>
+      <c r="J49" s="72">
+        <v>100</v>
+      </c>
+      <c r="K49" s="72">
+        <v>100</v>
       </c>
       <c r="L49" s="29">
-        <v>91.35</v>
+        <v>100</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.2">
@@ -4684,31 +4684,31 @@
       <c r="B50" s="49">
         <v>0</v>
       </c>
-      <c r="C50" s="2">
-        <v>0</v>
-      </c>
-      <c r="D50" s="2">
-        <v>0</v>
-      </c>
-      <c r="E50" s="2">
-        <v>0</v>
-      </c>
-      <c r="F50" s="2">
-        <v>0</v>
-      </c>
-      <c r="G50" s="2">
-        <v>0.01</v>
-      </c>
-      <c r="H50" s="2">
-        <v>0</v>
-      </c>
-      <c r="I50" s="2">
-        <v>0</v>
-      </c>
-      <c r="J50" s="2">
-        <v>0</v>
-      </c>
-      <c r="K50" s="2">
+      <c r="C50" s="72">
+        <v>0</v>
+      </c>
+      <c r="D50" s="72">
+        <v>0</v>
+      </c>
+      <c r="E50" s="72">
+        <v>0</v>
+      </c>
+      <c r="F50" s="72">
+        <v>0</v>
+      </c>
+      <c r="G50" s="72">
+        <v>0</v>
+      </c>
+      <c r="H50" s="72">
+        <v>0</v>
+      </c>
+      <c r="I50" s="72">
+        <v>0</v>
+      </c>
+      <c r="J50" s="72">
+        <v>0</v>
+      </c>
+      <c r="K50" s="72">
         <v>0</v>
       </c>
       <c r="L50" s="29">
@@ -4720,37 +4720,37 @@
         <v>15</v>
       </c>
       <c r="B51" s="49">
-        <v>0.01</v>
-      </c>
-      <c r="C51" s="2">
-        <v>0.08</v>
-      </c>
-      <c r="D51" s="2">
-        <v>0</v>
-      </c>
-      <c r="E51" s="2">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="F51" s="2">
-        <v>100</v>
-      </c>
-      <c r="G51" s="2">
-        <v>87.49</v>
-      </c>
-      <c r="H51" s="2">
-        <v>100</v>
-      </c>
-      <c r="I51" s="2">
-        <v>94.83</v>
-      </c>
-      <c r="J51" s="2">
-        <v>100</v>
-      </c>
-      <c r="K51" s="2">
-        <v>83.83</v>
+        <v>0</v>
+      </c>
+      <c r="C51" s="72">
+        <v>0.04</v>
+      </c>
+      <c r="D51" s="72">
+        <v>0</v>
+      </c>
+      <c r="E51" s="72">
+        <v>0</v>
+      </c>
+      <c r="F51" s="72">
+        <v>100</v>
+      </c>
+      <c r="G51" s="72">
+        <v>100</v>
+      </c>
+      <c r="H51" s="72">
+        <v>100</v>
+      </c>
+      <c r="I51" s="72">
+        <v>100</v>
+      </c>
+      <c r="J51" s="72">
+        <v>100</v>
+      </c>
+      <c r="K51" s="72">
+        <v>100</v>
       </c>
       <c r="L51" s="29">
-        <v>9.23</v>
+        <v>100</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.2">
@@ -4758,33 +4758,33 @@
         <v>16</v>
       </c>
       <c r="B52" s="49">
-        <v>0.02</v>
-      </c>
-      <c r="C52" s="2">
+        <v>0</v>
+      </c>
+      <c r="C52" s="72">
+        <v>0</v>
+      </c>
+      <c r="D52" s="72">
         <v>0.01</v>
       </c>
-      <c r="D52" s="2">
-        <v>0</v>
-      </c>
-      <c r="E52" s="2">
-        <v>0</v>
-      </c>
-      <c r="F52" s="2">
-        <v>0</v>
-      </c>
-      <c r="G52" s="2">
-        <v>0</v>
-      </c>
-      <c r="H52" s="2">
-        <v>0.01</v>
-      </c>
-      <c r="I52" s="2">
-        <v>0.01</v>
-      </c>
-      <c r="J52" s="2">
-        <v>0</v>
-      </c>
-      <c r="K52" s="2">
+      <c r="E52" s="72">
+        <v>0</v>
+      </c>
+      <c r="F52" s="72">
+        <v>0</v>
+      </c>
+      <c r="G52" s="72">
+        <v>0</v>
+      </c>
+      <c r="H52" s="72">
+        <v>0</v>
+      </c>
+      <c r="I52" s="72">
+        <v>0</v>
+      </c>
+      <c r="J52" s="72">
+        <v>0</v>
+      </c>
+      <c r="K52" s="72">
         <v>0</v>
       </c>
       <c r="L52" s="29">
@@ -4796,37 +4796,37 @@
         <v>17</v>
       </c>
       <c r="B53" s="49">
-        <v>15.74</v>
-      </c>
-      <c r="C53" s="2">
-        <v>70.92</v>
-      </c>
-      <c r="D53" s="2">
-        <v>100</v>
-      </c>
-      <c r="E53" s="2">
-        <v>95.53</v>
-      </c>
-      <c r="F53" s="2">
-        <v>100</v>
-      </c>
-      <c r="G53" s="2">
-        <v>98.97</v>
-      </c>
-      <c r="H53" s="2">
-        <v>100</v>
-      </c>
-      <c r="I53" s="2">
-        <v>96.41</v>
-      </c>
-      <c r="J53" s="2">
-        <v>100</v>
-      </c>
-      <c r="K53" s="2">
-        <v>95.75</v>
+        <v>16.489999999999998</v>
+      </c>
+      <c r="C53" s="72">
+        <v>87.75</v>
+      </c>
+      <c r="D53" s="72">
+        <v>100</v>
+      </c>
+      <c r="E53" s="72">
+        <v>100</v>
+      </c>
+      <c r="F53" s="72">
+        <v>100</v>
+      </c>
+      <c r="G53" s="72">
+        <v>100</v>
+      </c>
+      <c r="H53" s="72">
+        <v>100</v>
+      </c>
+      <c r="I53" s="72">
+        <v>100</v>
+      </c>
+      <c r="J53" s="72">
+        <v>100</v>
+      </c>
+      <c r="K53" s="72">
+        <v>100</v>
       </c>
       <c r="L53" s="29">
-        <v>99.26</v>
+        <v>100</v>
       </c>
     </row>
     <row r="54" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
